--- a/data/sources/countries/paraguay.xlsx
+++ b/data/sources/countries/paraguay.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI8"/>
+  <dimension ref="A1:BE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -827,7 +731,7 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>600</t>
         </is>
@@ -865,12 +769,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Adquisición completa de activos de Nidera</t>
+          <t>Adquisición Completa De Activos De Nidera</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Full acquisition of Nidera holdings</t>
+          <t>Full Acquisition Of Nidera Holdings</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -941,68 +845,18 @@
           <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf#page=189</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>https://www.clingendael.org/sites/default/files/2019-01/Report\_Assessing\_China\_Influence-in-Europe.pdf</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau\_2015\_Seeds\_\_Grain\_Trade\_\_and\_Power\_Off-land\_-\_Chinese\_Agribusiness\_in\_Global\_Agrarian\_Change-libre.pdf?1453313942=\&amp;response-content-disposition=inline%3B+filename%3DSeeds\_Grain\_Trade\_and\_Power\_Off\_land\_Chi.pdf\&amp;Expires=1752079385\&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi\~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD\~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU\~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L\~7mvowMCczMDdxaYIbjFXiScRrVuIQ\_\_\&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa\_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4\_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701\_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf\#page=189</t>
-        </is>
-      </c>
       <c r="BA2" t="n">
         <v>2</v>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>1</v>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
+        </is>
       </c>
       <c r="BD2" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
@@ -1035,7 +889,7 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>600</t>
         </is>
@@ -1073,12 +927,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Adquisición completa de activos de Nidera</t>
+          <t>Adquisición Completa De Activos De Nidera</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Full acquisition of Nidera holdings</t>
+          <t>Full Acquisition Of Nidera Holdings</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1101,76 +955,26 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>https://www.clingendael.org/sites/default/files/2019-01/Report\_Assessing\_China\_Influence-in-Europe.pdf</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau\_2015\_Seeds\_\_Grain\_Trade\_\_and\_Power\_Off-land\_-\_Chinese\_Agribusiness\_in\_Global\_Agrarian\_Change-libre.pdf?1453313942=\&amp;response-content-disposition=inline%3B+filename%3DSeeds\_Grain\_Trade\_and\_Power\_Off\_land\_Chi.pdf\&amp;Expires=1752079385\&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi\~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD\~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU\~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L\~7mvowMCczMDdxaYIbjFXiScRrVuIQ\_\_\&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa\_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4\_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701\_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf\#page=189</t>
         </is>
       </c>
       <c r="BA3" t="n">
         <v>2</v>
       </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>1</v>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
+        </is>
       </c>
       <c r="BD3" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
@@ -1203,7 +1007,7 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>600</t>
         </is>
@@ -1241,12 +1045,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Adquisición completa de activos de Nidera</t>
+          <t>Adquisición Completa De Activos De Nidera</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Full acquisition of Nidera holdings</t>
+          <t>Full Acquisition Of Nidera Holdings</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1269,76 +1073,26 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>https://www.clingendael.org/sites/default/files/2019-01/Report\_Assessing\_China\_Influence-in-Europe.pdf</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau\_2015\_Seeds\_\_Grain\_Trade\_\_and\_Power\_Off-land\_-\_Chinese\_Agribusiness\_in\_Global\_Agrarian\_Change-libre.pdf?1453313942=\&amp;response-content-disposition=inline%3B+filename%3DSeeds\_Grain\_Trade\_and\_Power\_Off\_land\_Chi.pdf\&amp;Expires=1752079385\&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi\~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD\~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU\~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L\~7mvowMCczMDdxaYIbjFXiScRrVuIQ\_\_\&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa\_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4\_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701\_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf\#page=189</t>
         </is>
       </c>
       <c r="BA4" t="n">
         <v>2</v>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
+        </is>
       </c>
       <c r="BD4" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
@@ -1371,7 +1125,7 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>600</t>
         </is>
@@ -1409,12 +1163,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Adquisición completa de activos de Nidera</t>
+          <t>Adquisición Completa De Activos De Nidera</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Full acquisition of Nidera holdings</t>
+          <t>Full Acquisition Of Nidera Holdings</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1437,76 +1191,26 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>https://www.clingendael.org/sites/default/files/2019-01/Report\_Assessing\_China\_Influence-in-Europe.pdf</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau\_2015\_Seeds\_\_Grain\_Trade\_\_and\_Power\_Off-land\_-\_Chinese\_Agribusiness\_in\_Global\_Agrarian\_Change-libre.pdf?1453313942=\&amp;response-content-disposition=inline%3B+filename%3DSeeds\_Grain\_Trade\_and\_Power\_Off\_land\_Chi.pdf\&amp;Expires=1752079385\&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi\~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD\~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU\~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L\~7mvowMCczMDdxaYIbjFXiScRrVuIQ\_\_\&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa\_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4\_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701\_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf\#page=189</t>
         </is>
       </c>
       <c r="BA5" t="n">
         <v>2</v>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
+        </is>
       </c>
       <c r="BD5" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
@@ -1539,7 +1243,7 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>600</t>
         </is>
@@ -1577,12 +1281,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Adquisición completa de activos de Nidera</t>
+          <t>Adquisición Completa De Activos De Nidera</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Full acquisition of Nidera holdings</t>
+          <t>Full Acquisition Of Nidera Holdings</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1605,76 +1309,26 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>https://www.clingendael.org/sites/default/files/2019-01/Report\_Assessing\_China\_Influence-in-Europe.pdf</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau\_2015\_Seeds\_\_Grain\_Trade\_\_and\_Power\_Off-land\_-\_Chinese\_Agribusiness\_in\_Global\_Agrarian\_Change-libre.pdf?1453313942=\&amp;response-content-disposition=inline%3B+filename%3DSeeds\_Grain\_Trade\_and\_Power\_Off\_land\_Chi.pdf\&amp;Expires=1752079385\&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi\~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD\~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU\~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L\~7mvowMCczMDdxaYIbjFXiScRrVuIQ\_\_\&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa\_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4\_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701\_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf\#page=189</t>
         </is>
       </c>
       <c r="BA6" t="n">
         <v>2</v>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>1</v>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
+        </is>
       </c>
       <c r="BD6" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
@@ -1707,7 +1361,7 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>600</t>
         </is>
@@ -1745,12 +1399,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Adquisición completa de activos de Nidera</t>
+          <t>Adquisición Completa De Activos De Nidera</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Full acquisition of Nidera holdings</t>
+          <t>Full Acquisition Of Nidera Holdings</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1773,76 +1427,26 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>https://www.clingendael.org/sites/default/files/2019-01/Report\_Assessing\_China\_Influence-in-Europe.pdf</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau\_2015\_Seeds\_\_Grain\_Trade\_\_and\_Power\_Off-land\_-\_Chinese\_Agribusiness\_in\_Global\_Agrarian\_Change-libre.pdf?1453313942=\&amp;response-content-disposition=inline%3B+filename%3DSeeds\_Grain\_Trade\_and\_Power\_Off\_land\_Chi.pdf\&amp;Expires=1752079385\&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi\~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD\~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU\~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L\~7mvowMCczMDdxaYIbjFXiScRrVuIQ\_\_\&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa\_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4\_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701\_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf\#page=189</t>
         </is>
       </c>
       <c r="BA7" t="n">
         <v>2</v>
       </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>1</v>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
+        </is>
       </c>
       <c r="BD7" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
@@ -1875,7 +1479,7 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>600</t>
         </is>
@@ -1913,12 +1517,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Adquisición completa de activos de Nidera Semillas</t>
+          <t>Adquisición Completa De Activos De Nidera Semillas</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Full acquisition of Nidera Semillas</t>
+          <t>Full Acquisition Of Nidera Semillas</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1989,38 +1593,23 @@
           <t>https://www.tandfonline.com/doi/full/10.1080/03066150.2018.1450242?casa_token=Cj4-5nZPnwcAAAAA%3AzYnNB3T3f934q4VQ8doM3sudGRHzvyAByl21yhlZb91YZCQIjXwFc_OxsZkmwCKbco5Pou2C0GlZ#d1e1201</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Paul Belesky and Geoffery Lawrence. (2024). “Chinese state capitalism and neomercantilism in the contemporary food regime: contradictions, continuity and change,” the Journal of Peasant Studies, 2018.</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>https://www.tandfonline.com/doi/full/10.1080/03066150.2018.1450242?casa\_token=Cj4-5nZPnwcAAAAA%3AzYnNB3T3f934q4VQ8doM3sudGRHzvyAByl21yhlZb91YZCQIjXwFc\_OxsZkmwCKbco5Pou2C0GlZ\#d1e1201</t>
-        </is>
-      </c>
       <c r="BA8" t="n">
         <v>3</v>
       </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>Syngenta (propiedad de ChemChina) completó la adquisición de Nidera Seeds de COFCO International en febrero 2018. Nidera Seeds tenía operaciones en Brasil, Argentina, Uruguay y Paraguay. Allison proporcionó fuente (iProfesional) indicando que el valor fue \~USD 3,000M para toda la operación, no USD 2M como aparece registrado. El monto de USD 2M es claramente incorrecto; posiblemente sea una estimación del componente Paraguay de una transacción global multimillonaria.</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>0</v>
       </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://www.syngenta.com/media/media-releases/2018/syngenta-completes-acquisition-nidera-seeds-cofco-international</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>https://www.world-grain.com/articles/9357-syngenta-finalizes-purchase-of-nidera-seeds-from-cofco</t>
+        </is>
+      </c>
       <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://www.syngenta.com/media/media-releases/2018/syngenta-completes-acquisition-nidera-seeds-cofco-international</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>https://www.world-grain.com/articles/9357-syngenta-finalizes-purchase-of-nidera-seeds-from-cofco</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
         <is>
           <t>https://www.iprofesional.com/negocios/263114-syngenta-completo-la-compra-de-nidera-por-un-valor-cercano-a-us3-000-millones</t>
         </is>

--- a/data/sources/countries/paraguay.xlsx
+++ b/data/sources/countries/paraguay.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE8"/>
+  <dimension ref="A1:BI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,22 +684,42 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>source4</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>source5</t>
         </is>
       </c>
     </row>
@@ -731,10 +750,8 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="G2" t="n">
+        <v>600</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -785,11 +802,13 @@
       <c r="R2" t="n">
         <v>15</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -845,22 +864,55 @@
           <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf#page=189</t>
         </is>
       </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>2</v>
       </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
       </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -889,10 +941,8 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="G3" t="n">
+        <v>600</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -943,11 +993,13 @@
       <c r="R3" t="n">
         <v>15</v>
       </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -963,22 +1015,95 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>https://www.clingendael.org/sites/default/files/2019-01/Report_Assessing_China_Influence-in-Europe.pdf</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau_2015_Seeds__Grain_Trade__and_Power_Off-land_-_Chinese_Agribusiness_in_Global_Agrarian_Change-libre.pdf?1453313942=&amp;response-content-disposition=inline%3B+filename%3DSeeds_Grain_Trade_and_Power_Off_land_Chi.pdf&amp;Expires=1752079385&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L~7mvowMCczMDdxaYIbjFXiScRrVuIQ__&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf#page=189</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
       </c>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1007,10 +1132,8 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="G4" t="n">
+        <v>600</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1061,11 +1184,13 @@
       <c r="R4" t="n">
         <v>15</v>
       </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -1081,22 +1206,95 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>https://www.clingendael.org/sites/default/files/2019-01/Report_Assessing_China_Influence-in-Europe.pdf</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau_2015_Seeds__Grain_Trade__and_Power_Off-land_-_Chinese_Agribusiness_in_Global_Agrarian_Change-libre.pdf?1453313942=&amp;response-content-disposition=inline%3B+filename%3DSeeds_Grain_Trade_and_Power_Off_land_Chi.pdf&amp;Expires=1752079385&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L~7mvowMCczMDdxaYIbjFXiScRrVuIQ__&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf#page=189</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>2</v>
       </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
       </c>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1125,10 +1323,8 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="G5" t="n">
+        <v>600</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1179,11 +1375,13 @@
       <c r="R5" t="n">
         <v>15</v>
       </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -1199,22 +1397,95 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>https://www.clingendael.org/sites/default/files/2019-01/Report_Assessing_China_Influence-in-Europe.pdf</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau_2015_Seeds__Grain_Trade__and_Power_Off-land_-_Chinese_Agribusiness_in_Global_Agrarian_Change-libre.pdf?1453313942=&amp;response-content-disposition=inline%3B+filename%3DSeeds_Grain_Trade_and_Power_Off_land_Chi.pdf&amp;Expires=1752079385&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L~7mvowMCczMDdxaYIbjFXiScRrVuIQ__&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf#page=189</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>2</v>
       </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
       </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1243,10 +1514,8 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="G6" t="n">
+        <v>600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1297,11 +1566,13 @@
       <c r="R6" t="n">
         <v>15</v>
       </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -1317,22 +1588,95 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>https://www.clingendael.org/sites/default/files/2019-01/Report_Assessing_China_Influence-in-Europe.pdf</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau_2015_Seeds__Grain_Trade__and_Power_Off-land_-_Chinese_Agribusiness_in_Global_Agrarian_Change-libre.pdf?1453313942=&amp;response-content-disposition=inline%3B+filename%3DSeeds_Grain_Trade_and_Power_Off_land_Chi.pdf&amp;Expires=1752079385&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L~7mvowMCczMDdxaYIbjFXiScRrVuIQ__&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf#page=189</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>2</v>
       </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
       </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1361,10 +1705,8 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="G7" t="n">
+        <v>600</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1415,11 +1757,13 @@
       <c r="R7" t="n">
         <v>15</v>
       </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -1435,22 +1779,95 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Matt Ferchen et al. (2024). “Assessing China’s Influence in Europe through Investments in Technology and Infrastructure. Four Cases.,” LeidenAsiaCentre, 2019.</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>https://www.clingendael.org/sites/default/files/2019-01/Report_Assessing_China_Influence-in-Europe.pdf</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Matthew Gaudreau. (2024). “Seeds, Grain Trade, and Power Off-land: Chinese Agribusiness in Global Agrarian Change,” Land grabbing, conflict and agrarian‐environmental transformations: perspectives from East and Southeast Asia, 2015.</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>https://d1wqtxts1xzle7.cloudfront.net/41353062/Gaudreau_2015_Seeds__Grain_Trade__and_Power_Off-land_-_Chinese_Agribusiness_in_Global_Agrarian_Change-libre.pdf?1453313942=&amp;response-content-disposition=inline%3B+filename%3DSeeds_Grain_Trade_and_Power_Off_land_Chi.pdf&amp;Expires=1752079385&amp;Signature=cPujdDusZsQ2bbBeKMkTkhjLbcjemZERuxbJsMrTwlBhH6LUF63TVQCZFxi5DSeTwR0vYq0SRLt5hIZi~SRkdasrT9lQJsuesOgRmFv24QCi21Kr2RoP4oiKRjFrq9vHzxk3NNzXNRgKEeopl7qDUbApQg56tVwqD~Xe2m8rloeMLnGcW604MlqwcyVPUawuCB0RpiU~iwPeJgrzt6vY3lXfZ5FSFkUf61yghID8jEp2bS2gcK8zmyHpFdKAirTgX5cmWcU3G0j2w0vfkGFXrN3uoo7WqMtDYSlHSdAJJCb9dZsJKRAd4g3L~7mvowMCczMDdxaYIbjFXiScRrVuIQ__&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Valdemar João Wesz Junior. (2024). “Soybean production in Paraguay: Agribusiness, economic change and agrarian transformations,” Journal of Agarian Change, 2021.</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/joac.12436?casa_token=DOuhpIK1s8kAAAAA%3ASkD2cLWTZ4_NVSXRQiUwySOS0fjdGnSyY6ZIQ7UVGviPzvTeyjdYrE7jHJVLGqHDvE089yrF28Qrkv4</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Eduardo Daniel Oviedo. (2024). “Argentine Soybean Exports to China. Myths and Realities in the Pampas Region,” LATIN AMERICAN EXPORTS TO CHINA. Local Experiences and Challenges, 2025.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Enrique-Peters/publication/392399701_PRESENTATION/links/684078e38a76251f22eb78b2/PRESENTATION.pdf#page=189</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>2</v>
       </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>COFCO completó la adquisición del 100% de Nidera en febrero 2017. Nidera tenía operaciones en Paraguay como parte de su red en el Cono Sur (Argentina, Uruguay, Paraguay). Allison sugiere eliminar la entrada: Nidera Seeds se vendió en 2018 a Syngenta y la cerealera nunca se construyó; no hay evidencia de que la operación siga activa en Paraguay. El monto de USD 15M no se pudo verificar como componente específico de Paraguay.</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://www.world-grain.com/articles/7793-cofco-completes-acquisition-of-nidera</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://www.cofcointernational.com/newsroom/acquisition-of-nidera-completed/</t>
         </is>
       </c>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1479,10 +1896,8 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="G8" t="n">
+        <v>600</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1533,11 +1948,13 @@
       <c r="R8" t="n">
         <v>2</v>
       </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -1593,27 +2010,210 @@
           <t>https://www.tandfonline.com/doi/full/10.1080/03066150.2018.1450242?casa_token=Cj4-5nZPnwcAAAAA%3AzYnNB3T3f934q4VQ8doM3sudGRHzvyAByl21yhlZb91YZCQIjXwFc_OxsZkmwCKbco5Pou2C0GlZ#d1e1201</t>
         </is>
       </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
         <v>3</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Syngenta (propiedad de ChemChina) completó la adquisición de Nidera Seeds de COFCO International en febrero 2018. Nidera Seeds tenía operaciones en Brasil, Argentina, Uruguay y Paraguay. Allison proporcionó fuente (iProfesional) indicando que el valor fue \~USD 3,000M para toda la operación, no USD 2M como aparece registrado. El monto de USD 2M es claramente incorrecto; posiblemente sea una estimación del componente Paraguay de una transacción global multimillonaria.</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
         <v>0</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://www.syngenta.com/media/media-releases/2018/syngenta-completes-acquisition-nidera-seeds-cofco-international</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>https://www.world-grain.com/articles/9357-syngenta-finalizes-purchase-of-nidera-seeds-from-cofco</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>https://www.iprofesional.com/negocios/263114-syngenta-completo-la-compra-de-nidera-por-un-valor-cercano-a-us3-000-millones</t>
         </is>
       </c>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PRY-0003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-25.416700, -55.016700</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>600</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PY-10</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Acereste</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Minería</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Planta siderúrgica en Yguazú</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Steel plant in Yguazú</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Yguazu, Alto Parana</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Greenfield</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Inversion aportada por Claire Espinosa y Allison Stronach, entrega del 20 de agosto de 2026. | SIN PUNTAJE DE FIABILIDAD: Claire y Allison lo dejaron a proposito para que lo asigne un revisor externo.</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>https://infonegocios.com.py/plus/desde-china-aceros-del-oriente-invierte-us-32-millones-en-yguazu-70-de-su-produccion-abastecera-al-mercado-brasileno</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>https://elnacional.com.py/economia/empresa-metalurgica-anuncia-instalacion-paraguay-inversion-usd-30-millones-n87100</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>https://www.fastmarkets.com/insights/china-origin-capital-plants-flags-in-paraguay-as-brazils-steel-doors-close/</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
